--- a/data/orders/2026-T4_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T4_declaration_tps_tvq.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Déclaration TPS-TVQ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dépenses" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00 &quot;$&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +67,30 @@
       <color rgb="FF595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +127,16 @@
         <fgColor rgb="FFEEF4FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9E7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -174,6 +207,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -537,9 +588,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F15"/>
+  <dimension ref="B2:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -641,13 +692,13 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>1199.09</v>
+        <v>2095.9</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>59.95</v>
+        <v>104.8</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>119.61</v>
+        <v>209.07</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -662,13 +713,13 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>1039.09</v>
+        <v>1872.9</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>55.56</v>
+        <v>96.8</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>110.89</v>
+        <v>193.1</v>
       </c>
     </row>
     <row r="14">
@@ -685,11 +736,288 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>SECTION B — DÉPENSES (taxes payées sur les achats et frais)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Montant HT ($)</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>TPS payée ($)</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>TVQ payée ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>CTI / RTI</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Dépenses (0 pièce)</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Aucune dépense : déposer les factures et reçus dans le dossier depenses/2026-T4/ du dépôt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>SECTION C — SOLDE À PAYER OU À RÉCLAMER</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="10" t="inlineStr"/>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>TPS ($)</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>TVQ ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="14" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Taxes perçues des clients (Shopify, ligne 105/205)</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="13" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>193.1</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="14" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Moins : taxes payées sur les dépenses</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="16" t="inlineStr"/>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Taxe nette (perçue − payée)</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="18" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>193.1</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>TPS : 96,80 $ à payer à Revenu Québec</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>TVQ : 193,10 $ à payer à Revenu Québec</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="9">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C26:D26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Fichier</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>Fournisseur</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>N° facture</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>Montant HT ($)</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>TPS payée ($)</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>TVQ payée ($)</t>
+        </is>
+      </c>
+      <c r="I1" s="21" t="inlineStr">
+        <is>
+          <t>Total ($)</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>Lu par</t>
+        </is>
+      </c>
+      <c r="K1" s="21" t="inlineStr">
+        <is>
+          <t>Remarques</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/data/orders/2026-T4_declaration_tps_tvq.xlsx
+++ b/data/orders/2026-T4_declaration_tps_tvq.xlsx
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>2095.9</v>
+        <v>3513.81</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>104.8</v>
+        <v>175.69</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>209.07</v>
+        <v>350.5</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>1872.9</v>
+        <v>3059.53</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>96.8</v>
+        <v>157.97</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>193.1</v>
+        <v>315.09</v>
       </c>
     </row>
     <row r="14">
@@ -839,10 +839,10 @@
       </c>
       <c r="D24" s="14" t="n"/>
       <c r="E24" s="13" t="n">
-        <v>96.8</v>
+        <v>157.97</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>193.1</v>
+        <v>315.09</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -869,16 +869,16 @@
       </c>
       <c r="D26" s="16" t="n"/>
       <c r="E26" s="18" t="n">
-        <v>96.8</v>
+        <v>157.97</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>193.1</v>
+        <v>315.09</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>TPS : 96,80 $ à payer à Revenu Québec</t>
+          <t>TPS : 157,97 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
@@ -889,7 +889,7 @@
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>TVQ : 193,10 $ à payer à Revenu Québec</t>
+          <t>TVQ : 315,09 $ à payer à Revenu Québec</t>
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
@@ -920,20 +920,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -954,40 +955,45 @@
       </c>
       <c r="D1" s="21" t="inlineStr">
         <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
           <t>N° facture</t>
         </is>
       </c>
-      <c r="E1" s="21" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="21" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
         <is>
           <t>Montant HT ($)</t>
         </is>
       </c>
-      <c r="G1" s="21" t="inlineStr">
+      <c r="H1" s="21" t="inlineStr">
         <is>
           <t>TPS payée ($)</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
+      <c r="I1" s="21" t="inlineStr">
         <is>
           <t>TVQ payée ($)</t>
         </is>
       </c>
-      <c r="I1" s="21" t="inlineStr">
+      <c r="J1" s="21" t="inlineStr">
         <is>
           <t>Total ($)</t>
         </is>
       </c>
-      <c r="J1" s="21" t="inlineStr">
+      <c r="K1" s="21" t="inlineStr">
         <is>
           <t>Lu par</t>
         </is>
       </c>
-      <c r="K1" s="21" t="inlineStr">
+      <c r="L1" s="21" t="inlineStr">
         <is>
           <t>Remarques</t>
         </is>
@@ -1003,18 +1009,19 @@
       <c r="C2" s="22" t="n"/>
       <c r="D2" s="22" t="n"/>
       <c r="E2" s="22" t="n"/>
-      <c r="F2" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="F2" s="22" t="n"/>
       <c r="G2" s="23" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="22" t="n"/>
+      <c r="I2" s="23" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" s="22" t="n"/>
       <c r="K2" s="22" t="n"/>
+      <c r="L2" s="22" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
